--- a/data/the-machine-learning-workflow--loans.xlsx
+++ b/data/the-machine-learning-workflow--loans.xlsx
@@ -43761,7 +43761,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Synthetic loan applications for Chapter 105 (The Machine Learning Workflow).</t>
+          <t>Synthetic loan applications for Chapter 109 (The Machine Learning Workflow).</t>
         </is>
       </c>
     </row>
